--- a/school_2/vor_spartac_2_ceilling.xlsx
+++ b/school_2/vor_spartac_2_ceilling.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="474" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="475" uniqueCount="114">
   <si>
     <r>
       <rPr>
@@ -6566,46 +6566,8 @@
     <t>2 этаж. Шпаклевка потолков финишная под покраску</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <rFont val="ГОСТ тип А"/>
-        <family val="2"/>
-        <charset val="204"/>
-      </rPr>
-      <t>Площадь,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="ГОСТ тип А"/>
-        <family val="2"/>
-        <charset val="204"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <rFont val="ГОСТ тип А"/>
-        <family val="2"/>
-        <charset val="204"/>
-      </rPr>
-      <t>м²
-По РД</t>
-    </r>
-  </si>
-  <si>
     <t>Площадь
 по полу</t>
-  </si>
-  <si>
-    <t>По вед-ти</t>
-  </si>
-  <si>
-    <t>По РД</t>
   </si>
   <si>
     <t>Номер помещения</t>
@@ -6614,7 +6576,47 @@
     <t>Площадь, м²</t>
   </si>
   <si>
-    <t>По в-ти</t>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <rFont val="ГОСТ тип А"/>
+        <family val="2"/>
+        <charset val="204"/>
+      </rPr>
+      <t>Площадь,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="ГОСТ тип А"/>
+        <family val="2"/>
+        <charset val="204"/>
+      </rPr>
+      <t>по исп схемам</t>
+    </r>
+  </si>
+  <si>
+    <t>по исп схема</t>
+  </si>
+  <si>
+    <t>По РД
+по полу</t>
+  </si>
+  <si>
+    <t>разница
+между полом и потолком</t>
+  </si>
+  <si>
+    <t>По в-ти
+потолка</t>
+  </si>
+  <si>
+    <t>По вед-ти(РД)
+потолка</t>
+  </si>
+  <si>
+    <t>Разница между полом и потолком</t>
   </si>
 </sst>
 </file>
@@ -6750,7 +6752,7 @@
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -6775,8 +6777,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="16">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -6954,26 +6968,13 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="105">
+  <cellXfs count="110">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -7112,7 +7113,6 @@
       <alignment horizontal="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -7137,47 +7137,10 @@
     <xf numFmtId="165" fontId="10" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
-    </xf>
     <xf numFmtId="3" fontId="4" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
@@ -7196,7 +7159,6 @@
     <xf numFmtId="164" fontId="4" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="11" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
@@ -7238,12 +7200,13 @@
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="9" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -7262,13 +7225,56 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="11" fillId="5" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="11" fillId="5" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="6" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="6" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -10144,7 +10150,7 @@
       </c>
     </row>
     <row r="149" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E149" s="62"/>
+      <c r="E149" s="56"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10177,13 +10183,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="96" t="s">
+      <c r="A1" s="82" t="s">
         <v>91</v>
       </c>
-      <c r="B1" s="97"/>
-      <c r="C1" s="97"/>
-      <c r="D1" s="97"/>
-      <c r="E1" s="98"/>
+      <c r="B1" s="83"/>
+      <c r="C1" s="83"/>
+      <c r="D1" s="83"/>
+      <c r="E1" s="84"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="24" t="s">
@@ -10203,101 +10209,101 @@
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A3" s="51" t="s">
+      <c r="A3" s="50" t="s">
         <v>70</v>
       </c>
-      <c r="B3" s="52" t="s">
+      <c r="B3" s="51" t="s">
         <v>102</v>
       </c>
-      <c r="C3" s="52" t="s">
+      <c r="C3" s="51" t="s">
         <v>71</v>
       </c>
-      <c r="D3" s="53">
+      <c r="D3" s="52">
         <v>1</v>
       </c>
-      <c r="E3" s="53">
+      <c r="E3" s="52">
         <f>Лист1!B31</f>
         <v>2126.1999999999998</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A4" s="54" t="s">
+      <c r="A4" s="53" t="s">
         <v>72</v>
       </c>
-      <c r="B4" s="52"/>
-      <c r="C4" s="55" t="s">
+      <c r="B4" s="51"/>
+      <c r="C4" s="54" t="s">
         <v>73</v>
       </c>
-      <c r="D4" s="56">
+      <c r="D4" s="55">
         <v>0.15</v>
       </c>
-      <c r="E4" s="56">
+      <c r="E4" s="55">
         <f>E3*D4</f>
         <v>318.92999999999995</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A5" s="54" t="s">
+      <c r="A5" s="53" t="s">
         <v>74</v>
       </c>
-      <c r="B5" s="52"/>
-      <c r="C5" s="55" t="s">
+      <c r="B5" s="51"/>
+      <c r="C5" s="54" t="s">
         <v>73</v>
       </c>
-      <c r="D5" s="56">
+      <c r="D5" s="55">
         <v>4.5</v>
       </c>
-      <c r="E5" s="56">
+      <c r="E5" s="55">
         <f>E3*D5</f>
         <v>9567.9</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A6" s="51" t="s">
+      <c r="A6" s="50" t="s">
         <v>75</v>
       </c>
-      <c r="B6" s="52" t="s">
+      <c r="B6" s="51" t="s">
         <v>103</v>
       </c>
-      <c r="C6" s="52" t="s">
+      <c r="C6" s="51" t="s">
         <v>71</v>
       </c>
-      <c r="D6" s="53">
+      <c r="D6" s="52">
         <v>1</v>
       </c>
-      <c r="E6" s="53">
+      <c r="E6" s="52">
         <f>E3</f>
         <v>2126.1999999999998</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A7" s="54" t="s">
+      <c r="A7" s="53" t="s">
         <v>76</v>
       </c>
-      <c r="B7" s="52"/>
-      <c r="C7" s="55" t="s">
+      <c r="B7" s="51"/>
+      <c r="C7" s="54" t="s">
         <v>73</v>
       </c>
-      <c r="D7" s="56">
+      <c r="D7" s="55">
         <v>1.8</v>
       </c>
-      <c r="E7" s="56">
+      <c r="E7" s="55">
         <f>E6*D7</f>
         <v>3827.16</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A8" s="54" t="s">
+      <c r="A8" s="53" t="s">
         <v>77</v>
       </c>
-      <c r="B8" s="52"/>
-      <c r="C8" s="55" t="s">
+      <c r="B8" s="51"/>
+      <c r="C8" s="54" t="s">
         <v>73</v>
       </c>
-      <c r="D8" s="56">
+      <c r="D8" s="55">
         <v>0.15</v>
       </c>
-      <c r="E8" s="56">
+      <c r="E8" s="55">
         <f>E6*D8</f>
         <v>318.92999999999995</v>
       </c>
@@ -10321,16 +10327,16 @@
     <col min="3" max="16384" width="9.140625" style="27"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="102" customFormat="1" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A1" s="49" t="s">
+    <row r="1" spans="1:2" s="79" customFormat="1" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A1" s="48" t="s">
         <v>90</v>
       </c>
-      <c r="B1" s="103" t="s">
+      <c r="B1" s="80" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A2" s="50">
+      <c r="A2" s="49">
         <v>2003</v>
       </c>
       <c r="B2" s="44">
@@ -10338,7 +10344,7 @@
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A3" s="50">
+      <c r="A3" s="49">
         <v>2009</v>
       </c>
       <c r="B3" s="45">
@@ -10346,7 +10352,7 @@
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A4" s="50">
+      <c r="A4" s="49">
         <v>2010</v>
       </c>
       <c r="B4" s="46">
@@ -10354,7 +10360,7 @@
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A5" s="50">
+      <c r="A5" s="49">
         <v>2017</v>
       </c>
       <c r="B5" s="45">
@@ -10362,7 +10368,7 @@
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A6" s="50">
+      <c r="A6" s="49">
         <v>2018</v>
       </c>
       <c r="B6" s="44">
@@ -10370,7 +10376,7 @@
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A7" s="50">
+      <c r="A7" s="49">
         <v>2020</v>
       </c>
       <c r="B7" s="44">
@@ -10378,7 +10384,7 @@
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A8" s="50">
+      <c r="A8" s="49">
         <v>2022</v>
       </c>
       <c r="B8" s="45">
@@ -10386,7 +10392,7 @@
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A9" s="50">
+      <c r="A9" s="49">
         <v>2026</v>
       </c>
       <c r="B9" s="44">
@@ -10394,7 +10400,7 @@
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A10" s="50">
+      <c r="A10" s="49">
         <v>2027</v>
       </c>
       <c r="B10" s="45">
@@ -10402,7 +10408,7 @@
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A11" s="50">
+      <c r="A11" s="49">
         <v>2028</v>
       </c>
       <c r="B11" s="44">
@@ -10410,7 +10416,7 @@
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A12" s="50">
+      <c r="A12" s="49">
         <v>2029</v>
       </c>
       <c r="B12" s="45">
@@ -10418,7 +10424,7 @@
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A13" s="50">
+      <c r="A13" s="49">
         <v>2032</v>
       </c>
       <c r="B13" s="44">
@@ -10426,7 +10432,7 @@
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A14" s="50">
+      <c r="A14" s="49">
         <v>2042</v>
       </c>
       <c r="B14" s="45">
@@ -10434,7 +10440,7 @@
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A15" s="50">
+      <c r="A15" s="49">
         <v>2043</v>
       </c>
       <c r="B15" s="44">
@@ -10442,7 +10448,7 @@
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A16" s="50">
+      <c r="A16" s="49">
         <v>2046</v>
       </c>
       <c r="B16" s="44">
@@ -10450,7 +10456,7 @@
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A17" s="50">
+      <c r="A17" s="49">
         <v>2049</v>
       </c>
       <c r="B17" s="45">
@@ -10458,7 +10464,7 @@
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A18" s="50">
+      <c r="A18" s="49">
         <v>2051</v>
       </c>
       <c r="B18" s="44">
@@ -10466,7 +10472,7 @@
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A19" s="50">
+      <c r="A19" s="49">
         <v>2052</v>
       </c>
       <c r="B19" s="45">
@@ -10474,7 +10480,7 @@
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A20" s="50">
+      <c r="A20" s="49">
         <v>2053</v>
       </c>
       <c r="B20" s="44">
@@ -10482,7 +10488,7 @@
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A21" s="50">
+      <c r="A21" s="49">
         <v>2054</v>
       </c>
       <c r="B21" s="45">
@@ -10490,7 +10496,7 @@
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A22" s="50">
+      <c r="A22" s="49">
         <v>2055</v>
       </c>
       <c r="B22" s="44">
@@ -10498,7 +10504,7 @@
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A23" s="50">
+      <c r="A23" s="49">
         <v>2057</v>
       </c>
       <c r="B23" s="44">
@@ -10506,7 +10512,7 @@
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A24" s="50">
+      <c r="A24" s="49">
         <v>2058</v>
       </c>
       <c r="B24" s="45">
@@ -10514,7 +10520,7 @@
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A25" s="50">
+      <c r="A25" s="49">
         <v>2062</v>
       </c>
       <c r="B25" s="44">
@@ -10522,7 +10528,7 @@
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A26" s="50">
+      <c r="A26" s="49">
         <v>2067</v>
       </c>
       <c r="B26" s="44">
@@ -10530,7 +10536,7 @@
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A27" s="50">
+      <c r="A27" s="49">
         <v>2068</v>
       </c>
       <c r="B27" s="45">
@@ -10538,7 +10544,7 @@
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A28" s="50">
+      <c r="A28" s="49">
         <v>2069</v>
       </c>
       <c r="B28" s="44">
@@ -10546,7 +10552,7 @@
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A29" s="50">
+      <c r="A29" s="49">
         <v>2070</v>
       </c>
       <c r="B29" s="45">
@@ -10554,7 +10560,7 @@
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A30" s="50">
+      <c r="A30" s="49">
         <v>2071</v>
       </c>
       <c r="B30" s="44">
@@ -10565,7 +10571,7 @@
       <c r="A31" s="47" t="s">
         <v>69</v>
       </c>
-      <c r="B31" s="93">
+      <c r="B31" s="78">
         <f>SUM(B2:B30)</f>
         <v>2126.1999999999998</v>
       </c>
@@ -10577,941 +10583,813 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I49"/>
+  <dimension ref="A1:G49"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.42578125" customWidth="1"/>
-    <col min="2" max="2" width="13.7109375" customWidth="1"/>
-    <col min="3" max="7" width="0" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="17.42578125" style="89" customWidth="1"/>
+    <col min="2" max="2" width="13.7109375" style="89" customWidth="1"/>
+    <col min="3" max="5" width="9.140625" style="89" customWidth="1"/>
+    <col min="6" max="6" width="14.28515625" style="89" customWidth="1"/>
+    <col min="7" max="16384" width="9.140625" style="89"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="A1" s="49" t="s">
+    <row r="1" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="A1" s="48" t="s">
         <v>90</v>
       </c>
-      <c r="B1" s="94" t="s">
+      <c r="B1" s="88" t="s">
+        <v>107</v>
+      </c>
+      <c r="C1" s="95" t="s">
+        <v>111</v>
+      </c>
+      <c r="D1" s="94"/>
+      <c r="E1" s="95" t="s">
         <v>104</v>
       </c>
-      <c r="C1" t="s">
+      <c r="F1" s="95" t="s">
         <v>110</v>
       </c>
-      <c r="D1" s="95" t="s">
-        <v>105</v>
-      </c>
-      <c r="H1" s="94" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="50">
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="49">
         <v>2003</v>
       </c>
-      <c r="B2" s="44">
+      <c r="B2" s="64">
+        <f>Лист1!B2</f>
         <v>217.89999999999998</v>
       </c>
-      <c r="C2" s="44">
+      <c r="C2" s="64">
         <v>218.2</v>
       </c>
-      <c r="D2" s="68">
-        <f>B2</f>
-        <v>217.89999999999998</v>
-      </c>
-      <c r="E2" s="68">
-        <f>B2-D2</f>
+      <c r="D2" s="94"/>
+      <c r="E2" s="64">
+        <v>218.2</v>
+      </c>
+      <c r="F2" s="96">
+        <f>C2-E2</f>
         <v>0</v>
       </c>
-      <c r="G2" s="68"/>
-      <c r="H2" s="44">
-        <v>218.2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="50">
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="49">
         <v>2009</v>
       </c>
-      <c r="B3" s="45">
+      <c r="B3" s="64">
+        <f>Лист1!B3</f>
         <v>8.9</v>
       </c>
-      <c r="C3" s="45">
+      <c r="C3" s="64">
         <v>10.3</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="94"/>
+      <c r="E3" s="64">
         <v>10.3</v>
       </c>
-      <c r="E3" s="68">
-        <f>B3-D3</f>
-        <v>-1.4000000000000004</v>
-      </c>
-      <c r="G3" s="68"/>
-      <c r="H3" s="45">
-        <v>10.3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="50">
+      <c r="F3" s="96">
+        <f t="shared" ref="F3:F30" si="0">C3-E3</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="49">
         <v>2010</v>
       </c>
-      <c r="B4" s="46">
+      <c r="B4" s="64">
+        <f>Лист1!B4</f>
         <v>21.6</v>
       </c>
-      <c r="C4" s="46">
+      <c r="C4" s="91">
         <v>23.5</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="94"/>
+      <c r="E4" s="91">
         <v>23.5</v>
       </c>
-      <c r="E4" s="68">
-        <f>B4-D4</f>
-        <v>-1.8999999999999986</v>
-      </c>
-      <c r="G4" s="68"/>
-      <c r="H4" s="46">
-        <v>23.5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="50">
+      <c r="F4" s="96">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="97">
         <v>2017</v>
       </c>
-      <c r="B5" s="45">
+      <c r="B5" s="98">
+        <f>Лист1!B5</f>
         <v>236.70000000000002</v>
       </c>
-      <c r="C5" s="45">
+      <c r="C5" s="98">
         <f>478.8</f>
         <v>478.8</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="99"/>
+      <c r="E5" s="98">
         <v>237.9</v>
       </c>
-      <c r="E5" s="68">
-        <f>B5-D5</f>
-        <v>-1.1999999999999886</v>
-      </c>
-      <c r="G5" s="68"/>
-      <c r="H5" s="45">
-        <v>237.9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="50">
+      <c r="F5" s="100">
+        <f t="shared" si="0"/>
+        <v>240.9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="49">
         <v>2018</v>
       </c>
-      <c r="B6" s="44">
+      <c r="B6" s="64">
+        <f>Лист1!B6</f>
         <v>18.900000000000002</v>
       </c>
-      <c r="C6" s="44">
+      <c r="C6" s="64">
         <v>19.600000000000001</v>
       </c>
-      <c r="D6" s="68">
-        <f>B6</f>
-        <v>18.900000000000002</v>
-      </c>
-      <c r="E6" s="68">
-        <f>B6-D6</f>
+      <c r="D6" s="94"/>
+      <c r="E6" s="64">
+        <v>19.600000000000001</v>
+      </c>
+      <c r="F6" s="96">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G6" s="68"/>
-      <c r="H6" s="44">
-        <v>19.600000000000001</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="50">
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="49">
         <v>2020</v>
       </c>
-      <c r="B7" s="44">
+      <c r="B7" s="64">
+        <f>Лист1!B7</f>
         <v>9.6000000000000014</v>
       </c>
-      <c r="C7" s="44">
+      <c r="C7" s="64">
         <v>10.3</v>
       </c>
-      <c r="D7" s="68">
-        <f>B7</f>
-        <v>9.6000000000000014</v>
-      </c>
-      <c r="E7" s="68">
-        <f>B7-D7</f>
+      <c r="D7" s="94"/>
+      <c r="E7" s="64">
+        <v>10.3</v>
+      </c>
+      <c r="F7" s="96">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G7" s="68"/>
-      <c r="H7" s="44">
-        <v>10.3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="50">
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="49">
         <v>2022</v>
       </c>
-      <c r="B8" s="45">
+      <c r="B8" s="64">
+        <f>Лист1!B8</f>
         <v>471.2</v>
       </c>
-      <c r="C8" s="45">
+      <c r="C8" s="64">
         <f>478.7</f>
         <v>478.7</v>
       </c>
-      <c r="D8">
+      <c r="D8" s="94"/>
+      <c r="E8" s="64">
         <v>476.6</v>
       </c>
-      <c r="E8" s="68">
-        <f>B8-D8</f>
-        <v>-5.4000000000000341</v>
-      </c>
-      <c r="G8" s="68"/>
-      <c r="H8" s="45">
-        <v>476.6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="50">
+      <c r="F8" s="96">
+        <f t="shared" si="0"/>
+        <v>2.0999999999999659</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="49">
         <v>2026</v>
       </c>
-      <c r="B9" s="44">
+      <c r="B9" s="64">
+        <f>Лист1!B9</f>
         <v>15.6</v>
       </c>
-      <c r="C9" s="44">
+      <c r="C9" s="64">
         <v>16.600000000000001</v>
       </c>
-      <c r="D9" s="68">
-        <f t="shared" ref="D9:D15" si="0">B9</f>
-        <v>15.6</v>
-      </c>
-      <c r="E9" s="68">
-        <f>B9-D9</f>
+      <c r="D9" s="94"/>
+      <c r="E9" s="64">
+        <v>16.600000000000001</v>
+      </c>
+      <c r="F9" s="96">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G9" s="68"/>
-      <c r="H9" s="44">
-        <v>16.600000000000001</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="50">
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="49">
         <v>2027</v>
       </c>
-      <c r="B10" s="45">
+      <c r="B10" s="64">
+        <f>Лист1!B10</f>
         <v>7.6</v>
       </c>
-      <c r="C10" s="45">
+      <c r="C10" s="64">
         <v>8.1</v>
       </c>
-      <c r="D10" s="68">
+      <c r="D10" s="94"/>
+      <c r="E10" s="64">
+        <v>8.1</v>
+      </c>
+      <c r="F10" s="96">
         <f t="shared" si="0"/>
-        <v>7.6</v>
-      </c>
-      <c r="E10" s="68">
-        <f>B10-D10</f>
         <v>0</v>
       </c>
-      <c r="G10" s="68"/>
-      <c r="H10" s="45">
-        <v>8.1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="50">
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="49">
         <v>2028</v>
       </c>
-      <c r="B11" s="44">
+      <c r="B11" s="64">
+        <f>Лист1!B11</f>
         <v>19</v>
       </c>
-      <c r="C11" s="44">
+      <c r="C11" s="64">
         <v>19.8</v>
       </c>
-      <c r="D11" s="68">
+      <c r="D11" s="94"/>
+      <c r="E11" s="64">
+        <v>19.8</v>
+      </c>
+      <c r="F11" s="96">
         <f t="shared" si="0"/>
-        <v>19</v>
-      </c>
-      <c r="E11" s="68">
-        <f>B11-D11</f>
         <v>0</v>
       </c>
-      <c r="G11" s="68"/>
-      <c r="H11" s="44">
-        <v>19.8</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="50">
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="49">
         <v>2029</v>
       </c>
-      <c r="B12" s="45">
+      <c r="B12" s="64">
+        <f>Лист1!B12</f>
         <v>7.2999999999999989</v>
       </c>
-      <c r="C12" s="45">
+      <c r="C12" s="64">
         <v>8.1999999999999993</v>
       </c>
-      <c r="D12" s="68">
+      <c r="D12" s="94"/>
+      <c r="E12" s="64">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="F12" s="96">
         <f t="shared" si="0"/>
-        <v>7.2999999999999989</v>
-      </c>
-      <c r="E12" s="68">
-        <f>B12-D12</f>
         <v>0</v>
       </c>
-      <c r="G12" s="68"/>
-      <c r="H12" s="45">
-        <v>8.1999999999999993</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="50">
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="49">
         <v>2032</v>
       </c>
-      <c r="B13" s="44">
+      <c r="B13" s="64">
+        <f>Лист1!B13</f>
         <v>19.5</v>
       </c>
-      <c r="C13" s="44">
+      <c r="C13" s="64">
         <v>20.100000000000001</v>
       </c>
-      <c r="D13" s="68">
+      <c r="D13" s="94"/>
+      <c r="E13" s="64">
+        <v>20.100000000000001</v>
+      </c>
+      <c r="F13" s="96">
         <f t="shared" si="0"/>
-        <v>19.5</v>
-      </c>
-      <c r="E13" s="68">
-        <f>B13-D13</f>
         <v>0</v>
       </c>
-      <c r="G13" s="68"/>
-      <c r="H13" s="44">
-        <v>20.100000000000001</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="50">
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="49">
         <v>2042</v>
       </c>
-      <c r="B14" s="45">
+      <c r="B14" s="64">
+        <f>Лист1!B14</f>
         <v>101.8</v>
       </c>
-      <c r="C14" s="45">
+      <c r="C14" s="64">
         <v>103.6</v>
       </c>
-      <c r="D14" s="68">
+      <c r="D14" s="94"/>
+      <c r="E14" s="64">
+        <v>103.6</v>
+      </c>
+      <c r="F14" s="96">
         <f t="shared" si="0"/>
-        <v>101.8</v>
-      </c>
-      <c r="E14" s="68">
-        <f>B14-D14</f>
         <v>0</v>
       </c>
-      <c r="G14" s="68"/>
-      <c r="H14" s="45">
-        <v>103.6</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="50">
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="49">
         <v>2043</v>
       </c>
-      <c r="B15" s="44">
+      <c r="B15" s="64">
+        <f>Лист1!B15</f>
         <v>10.3</v>
       </c>
-      <c r="C15" s="44">
+      <c r="C15" s="64">
         <v>10.4</v>
       </c>
-      <c r="D15" s="68">
+      <c r="D15" s="94"/>
+      <c r="E15" s="64">
+        <v>10.4</v>
+      </c>
+      <c r="F15" s="96">
         <f t="shared" si="0"/>
-        <v>10.3</v>
-      </c>
-      <c r="E15" s="68">
-        <f>B15-D15</f>
         <v>0</v>
       </c>
-      <c r="G15" s="68"/>
-      <c r="H15" s="44">
-        <v>10.4</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="50">
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="97">
         <v>2046</v>
       </c>
-      <c r="B16" s="44">
+      <c r="B16" s="98">
+        <f>Лист1!B16</f>
         <v>162.10000000000002</v>
       </c>
-      <c r="C16" s="44">
+      <c r="C16" s="98">
         <f>326</f>
         <v>326</v>
       </c>
-      <c r="D16">
+      <c r="D16" s="99"/>
+      <c r="E16" s="98">
         <v>163.30000000000001</v>
       </c>
-      <c r="E16" s="68">
-        <f>B16-D16</f>
-        <v>-1.1999999999999886</v>
-      </c>
-      <c r="G16" s="68"/>
-      <c r="H16" s="44">
-        <v>163.30000000000001</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="50">
+      <c r="F16" s="100">
+        <f t="shared" si="0"/>
+        <v>162.69999999999999</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="97">
         <v>2049</v>
       </c>
-      <c r="B17" s="45">
+      <c r="B17" s="98">
+        <f>Лист1!B17</f>
         <v>127.00000000000001</v>
       </c>
-      <c r="C17" s="45">
+      <c r="C17" s="98">
         <v>256.2</v>
       </c>
-      <c r="D17">
+      <c r="D17" s="99"/>
+      <c r="E17" s="98">
         <v>128.30000000000001</v>
       </c>
-      <c r="E17" s="68">
-        <f>B17-D17</f>
-        <v>-1.2999999999999972</v>
-      </c>
-      <c r="G17" s="68"/>
-      <c r="H17" s="45">
-        <v>128.30000000000001</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="50">
+      <c r="F17" s="100">
+        <f t="shared" si="0"/>
+        <v>127.89999999999998</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="49">
         <v>2051</v>
       </c>
-      <c r="B18" s="44">
+      <c r="B18" s="64">
+        <f>Лист1!B18</f>
         <v>21.4</v>
       </c>
-      <c r="C18" s="44">
+      <c r="C18" s="64">
         <v>22.2</v>
       </c>
-      <c r="D18" s="68">
-        <f t="shared" ref="D18:D22" si="1">B18</f>
-        <v>21.4</v>
-      </c>
-      <c r="E18" s="68">
-        <f>B18-D18</f>
+      <c r="D18" s="94"/>
+      <c r="E18" s="64">
+        <v>22.2</v>
+      </c>
+      <c r="F18" s="96">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G18" s="68"/>
-      <c r="H18" s="44">
-        <v>22.2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="50">
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="49">
         <v>2052</v>
       </c>
-      <c r="B19" s="45">
+      <c r="B19" s="64">
+        <f>Лист1!B19</f>
         <v>4</v>
       </c>
-      <c r="C19" s="45">
+      <c r="C19" s="64">
         <v>4.4000000000000004</v>
       </c>
-      <c r="D19" s="68">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="E19" s="68">
-        <f>B19-D19</f>
+      <c r="D19" s="94"/>
+      <c r="E19" s="64">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="F19" s="96">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G19" s="68"/>
-      <c r="H19" s="45">
-        <v>4.4000000000000004</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="50">
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="49">
         <v>2053</v>
       </c>
-      <c r="B20" s="44">
+      <c r="B20" s="64">
+        <f>Лист1!B20</f>
         <v>5.3</v>
       </c>
-      <c r="C20" s="44">
+      <c r="C20" s="64">
         <v>5.6</v>
       </c>
-      <c r="D20" s="68">
-        <f t="shared" si="1"/>
-        <v>5.3</v>
-      </c>
-      <c r="E20" s="68">
-        <f>B20-D20</f>
+      <c r="D20" s="94"/>
+      <c r="E20" s="64">
+        <v>5.6</v>
+      </c>
+      <c r="F20" s="96">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G20" s="68"/>
-      <c r="H20" s="44">
-        <v>5.6</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="50">
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="49">
         <v>2054</v>
       </c>
-      <c r="B21" s="45">
+      <c r="B21" s="64">
+        <f>Лист1!B21</f>
         <v>20.6</v>
       </c>
-      <c r="C21" s="45">
+      <c r="C21" s="64">
         <v>22.1</v>
       </c>
-      <c r="D21" s="68">
-        <f t="shared" si="1"/>
-        <v>20.6</v>
-      </c>
-      <c r="E21" s="68">
-        <f>B21-D21</f>
+      <c r="D21" s="94"/>
+      <c r="E21" s="64">
+        <v>22.1</v>
+      </c>
+      <c r="F21" s="96">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G21" s="68"/>
-      <c r="H21" s="45">
-        <v>22.1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="50">
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="49">
         <v>2055</v>
       </c>
-      <c r="B22" s="44">
+      <c r="B22" s="64">
+        <f>Лист1!B22</f>
         <v>8.6000000000000014</v>
       </c>
-      <c r="C22" s="44">
+      <c r="C22" s="64">
         <v>10.3</v>
       </c>
-      <c r="D22" s="68">
-        <f t="shared" si="1"/>
-        <v>8.6000000000000014</v>
-      </c>
-      <c r="E22" s="68">
-        <f>B22-D22</f>
+      <c r="D22" s="94"/>
+      <c r="E22" s="64">
+        <v>10.3</v>
+      </c>
+      <c r="F22" s="96">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G22" s="68"/>
-      <c r="H22" s="44">
-        <v>10.3</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="50">
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="49">
         <v>2057</v>
       </c>
-      <c r="B23" s="44">
+      <c r="B23" s="64">
+        <f>Лист1!B23</f>
         <v>18</v>
       </c>
-      <c r="C23" s="44">
+      <c r="C23" s="64">
         <v>19.899999999999999</v>
       </c>
-      <c r="D23" s="68">
-        <f t="shared" ref="D23:D24" si="2">B23</f>
-        <v>18</v>
-      </c>
-      <c r="E23" s="68">
-        <f>B23-D23</f>
+      <c r="D23" s="94"/>
+      <c r="E23" s="64">
+        <v>19.899999999999999</v>
+      </c>
+      <c r="F23" s="96">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G23" s="68"/>
-      <c r="H23" s="44">
-        <v>19.899999999999999</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="50">
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="49">
         <v>2058</v>
       </c>
-      <c r="B24" s="45">
+      <c r="B24" s="64">
+        <f>Лист1!B24</f>
         <v>34.299999999999997</v>
       </c>
-      <c r="C24" s="45">
+      <c r="C24" s="64">
         <v>35.799999999999997</v>
       </c>
-      <c r="D24" s="68">
-        <f t="shared" si="2"/>
-        <v>34.299999999999997</v>
-      </c>
-      <c r="E24" s="68">
-        <f>B24-D24</f>
+      <c r="D24" s="94"/>
+      <c r="E24" s="64">
+        <v>35.799999999999997</v>
+      </c>
+      <c r="F24" s="96">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G24" s="68"/>
-      <c r="H24" s="45">
-        <v>35.799999999999997</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="50">
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="97">
         <v>2062</v>
       </c>
-      <c r="B25" s="44">
+      <c r="B25" s="98">
+        <f>Лист1!B25</f>
         <v>212.7</v>
       </c>
-      <c r="C25" s="44">
+      <c r="C25" s="98">
         <f>426.5</f>
         <v>426.5</v>
       </c>
-      <c r="D25">
+      <c r="D25" s="99"/>
+      <c r="E25" s="98">
         <v>213.5</v>
       </c>
-      <c r="E25" s="68">
-        <f>B25-D25</f>
-        <v>-0.80000000000001137</v>
-      </c>
-      <c r="G25" s="68"/>
-      <c r="H25" s="44">
-        <v>213.5</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="50">
+      <c r="F25" s="100">
+        <f t="shared" si="0"/>
+        <v>213</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="49">
         <v>2067</v>
       </c>
-      <c r="B26" s="44">
+      <c r="B26" s="64">
+        <f>Лист1!B26</f>
         <v>89.6</v>
       </c>
-      <c r="C26" s="44">
+      <c r="C26" s="64">
         <v>90.8</v>
       </c>
-      <c r="D26" s="68">
-        <f>B26</f>
-        <v>89.6</v>
-      </c>
-      <c r="E26" s="68">
-        <f>B26-D26</f>
+      <c r="D26" s="94"/>
+      <c r="E26" s="64">
+        <v>90.8</v>
+      </c>
+      <c r="F26" s="96">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G26" s="68"/>
-      <c r="H26" s="44">
-        <v>90.8</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="50">
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="49">
         <v>2068</v>
       </c>
-      <c r="B27" s="45">
+      <c r="B27" s="64">
+        <f>Лист1!B27</f>
         <v>111.8</v>
       </c>
-      <c r="C27" s="45">
+      <c r="C27" s="64">
         <v>112.7</v>
       </c>
-      <c r="D27" s="68">
-        <f t="shared" ref="D27:D28" si="3">B27</f>
-        <v>111.8</v>
-      </c>
-      <c r="E27" s="68">
-        <f>B27-D27</f>
+      <c r="D27" s="94"/>
+      <c r="E27" s="64">
+        <v>112.7</v>
+      </c>
+      <c r="F27" s="96">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G27" s="68"/>
-      <c r="H27" s="45">
-        <v>112.7</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="50">
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="49">
         <v>2069</v>
       </c>
-      <c r="B28" s="44">
+      <c r="B28" s="64">
+        <f>Лист1!B28</f>
         <v>3.1</v>
       </c>
-      <c r="C28" s="44">
+      <c r="C28" s="64">
         <v>3.2</v>
       </c>
-      <c r="D28" s="68">
-        <f t="shared" si="3"/>
-        <v>3.1</v>
-      </c>
-      <c r="E28" s="68">
-        <f>B28-D28</f>
+      <c r="D28" s="94"/>
+      <c r="E28" s="64">
+        <v>3.2</v>
+      </c>
+      <c r="F28" s="96">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G28" s="68"/>
-      <c r="H28" s="44">
-        <v>3.2</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="50">
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="49">
         <v>2070</v>
       </c>
-      <c r="B29" s="45">
+      <c r="B29" s="64">
+        <f>Лист1!B29</f>
         <v>13.700000000000001</v>
       </c>
-      <c r="C29" s="45">
+      <c r="C29" s="64">
         <v>15.3</v>
       </c>
-      <c r="D29" s="68">
-        <f>B29</f>
-        <v>13.700000000000001</v>
-      </c>
-      <c r="E29" s="68">
-        <f>B29-D29</f>
+      <c r="D29" s="94"/>
+      <c r="E29" s="64">
+        <v>15.3</v>
+      </c>
+      <c r="F29" s="96">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G29" s="68"/>
-      <c r="H29" s="45">
-        <v>15.3</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="50">
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="97">
         <v>2071</v>
       </c>
-      <c r="B30" s="44">
+      <c r="B30" s="98">
+        <f>Лист1!B30</f>
         <v>128.1</v>
       </c>
-      <c r="C30" s="44">
+      <c r="C30" s="98">
         <v>257.10000000000002</v>
       </c>
-      <c r="D30">
+      <c r="D30" s="99"/>
+      <c r="E30" s="98">
         <v>128.9</v>
       </c>
-      <c r="E30" s="68">
-        <f>B30-D30</f>
-        <v>-0.80000000000001137</v>
-      </c>
-      <c r="G30" s="68"/>
-      <c r="H30" s="44">
-        <v>128.9</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A31" s="47" t="s">
+      <c r="F30" s="100">
+        <f t="shared" si="0"/>
+        <v>128.20000000000002</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="92" t="s">
         <v>69</v>
       </c>
-      <c r="B31" s="48">
+      <c r="B31" s="93">
         <f>SUM(B2:B30)</f>
         <v>2126.1999999999998</v>
       </c>
-      <c r="D31" s="48">
-        <f>SUM(D2:D30)</f>
-        <v>2140.1999999999994</v>
-      </c>
-      <c r="E31" s="68">
-        <f>B31-D31</f>
-        <v>-13.999999999999545</v>
-      </c>
-      <c r="G31" s="68"/>
-    </row>
-    <row r="32" spans="1:8" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="33" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="50">
+      <c r="C31" s="93">
+        <f t="shared" ref="C31:E31" si="1">SUM(C2:C30)</f>
+        <v>3034.3</v>
+      </c>
+      <c r="D31" s="93">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="E31" s="93">
+        <f t="shared" si="1"/>
+        <v>2159.5</v>
+      </c>
+      <c r="F31" s="94"/>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" s="49">
         <v>2008</v>
       </c>
-      <c r="B33" s="44">
+      <c r="B33" s="64">
         <v>57.099999999999994</v>
       </c>
-      <c r="C33" s="44">
+      <c r="C33" s="64">
         <v>40.299999999999997</v>
       </c>
-      <c r="D33">
+      <c r="E33" s="89">
         <v>31.5</v>
       </c>
-      <c r="E33" s="68">
-        <f>B33-D33</f>
-        <v>25.599999999999994</v>
-      </c>
-      <c r="G33" s="68"/>
-    </row>
-    <row r="34" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="50">
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34" s="49">
         <v>2019</v>
       </c>
-      <c r="B34" s="44">
+      <c r="B34" s="64">
         <v>55.6</v>
       </c>
-      <c r="C34" s="44">
+      <c r="C34" s="64">
         <f>40.6+15</f>
         <v>55.6</v>
       </c>
-      <c r="D34">
+      <c r="E34" s="89">
         <v>38</v>
       </c>
-      <c r="E34" s="68">
-        <f>B34-D34</f>
-        <v>17.600000000000001</v>
-      </c>
-      <c r="G34" s="68"/>
-    </row>
-    <row r="35" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="50">
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A35" s="49">
         <v>2023</v>
       </c>
-      <c r="B35" s="44">
+      <c r="B35" s="64">
         <v>23.4</v>
       </c>
-      <c r="C35" s="44">
+      <c r="C35" s="64">
         <v>23.4</v>
       </c>
-      <c r="D35">
+      <c r="E35" s="89">
         <v>28.9</v>
       </c>
-      <c r="E35" s="68">
-        <f>B35-D35</f>
-        <v>-5.5</v>
-      </c>
-      <c r="G35" s="68"/>
-    </row>
-    <row r="36" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="50">
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36" s="49">
         <v>2024</v>
       </c>
-      <c r="B36" s="44">
+      <c r="B36" s="64">
         <v>67.599999999999994</v>
       </c>
-      <c r="C36" s="44">
+      <c r="C36" s="64">
         <f>52.6+15</f>
         <v>67.599999999999994</v>
       </c>
-      <c r="D36">
+      <c r="E36" s="89">
         <v>28.9</v>
       </c>
-      <c r="E36" s="68">
-        <f>B36-D36</f>
-        <v>38.699999999999996</v>
-      </c>
-      <c r="G36" s="68"/>
-    </row>
-    <row r="37" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="50">
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A37" s="49">
         <v>2044</v>
       </c>
-      <c r="B37" s="44">
+      <c r="B37" s="64">
         <v>63.6</v>
       </c>
-      <c r="C37" s="44">
+      <c r="C37" s="64">
         <f>43.6+20</f>
         <v>63.6</v>
       </c>
-      <c r="D37">
+      <c r="E37" s="89">
         <v>34.700000000000003</v>
       </c>
-      <c r="E37" s="68">
-        <f>B37-D37</f>
-        <v>28.9</v>
-      </c>
-      <c r="G37" s="68"/>
-    </row>
-    <row r="38" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="50">
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A38" s="49">
         <v>2056</v>
       </c>
-      <c r="B38" s="44">
+      <c r="B38" s="64">
         <v>50.4</v>
       </c>
-      <c r="C38" s="44">
+      <c r="C38" s="64">
         <f>30.4+20</f>
         <v>50.4</v>
       </c>
-      <c r="D38">
+      <c r="E38" s="89">
         <v>33.9</v>
       </c>
-      <c r="E38" s="68">
-        <f>B38-D38</f>
-        <v>16.5</v>
-      </c>
-      <c r="G38" s="68"/>
-    </row>
-    <row r="39" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="50">
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A39" s="49">
         <v>2063</v>
       </c>
-      <c r="B39" s="44">
+      <c r="B39" s="64">
         <v>66.099999999999994</v>
       </c>
-      <c r="C39" s="44">
+      <c r="C39" s="64">
         <f>23.4+22.7+20</f>
         <v>66.099999999999994</v>
       </c>
-      <c r="D39">
+      <c r="E39" s="89">
         <v>29.6</v>
       </c>
-      <c r="E39" s="68">
-        <f>B39-D39</f>
-        <v>36.499999999999993</v>
-      </c>
-      <c r="G39" s="68"/>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B40">
-        <v>3418.18</v>
-      </c>
-      <c r="D40">
-        <v>3418.18</v>
-      </c>
-      <c r="E40">
-        <v>3418.18</v>
-      </c>
-      <c r="H40" t="s">
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F40" s="89" t="s">
         <v>94</v>
       </c>
-      <c r="I40" s="68">
+      <c r="G40" s="90">
         <f>B23+B24+B25</f>
         <v>265</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B41" s="68">
-        <f>B31-B40</f>
-        <v>-1291.98</v>
-      </c>
-      <c r="D41" s="68">
-        <f>D31-D40</f>
-        <v>-1277.9800000000005</v>
-      </c>
-      <c r="E41" s="68">
-        <f>E31-E40</f>
-        <v>-3432.1799999999994</v>
-      </c>
-      <c r="G41" s="68"/>
-      <c r="H41" t="s">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B41" s="90"/>
+      <c r="E41" s="90"/>
+      <c r="F41" s="89" t="s">
         <v>95</v>
       </c>
-      <c r="I41" s="68">
+      <c r="G41" s="90">
         <f>SUM(B16:B22)+B28</f>
         <v>352.10000000000008</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="H42" t="s">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F42" s="89" t="s">
         <v>96</v>
       </c>
-      <c r="I42" s="68">
+      <c r="G42" s="90">
         <f>B14+B15+B30</f>
         <v>240.2</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="H43" t="s">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F43" s="89" t="s">
         <v>97</v>
       </c>
-      <c r="I43" s="68">
+      <c r="G43" s="90">
         <f>SUM(B8:B13)+B26+B27</f>
         <v>741.6</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="H44" t="s">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F44" s="89" t="s">
         <v>98</v>
       </c>
-      <c r="I44" s="68">
+      <c r="G44" s="90">
         <f>SUM(B5:B7)+B29</f>
         <v>278.90000000000003</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="H45" t="s">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F45" s="89" t="s">
         <v>99</v>
       </c>
-      <c r="I45" s="68">
+      <c r="G45" s="90">
         <f>SUM(B2:B4)</f>
         <v>248.39999999999998</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="I46" s="68">
-        <f>SUM(I40:I45)</f>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G46" s="90">
+        <f>SUM(G40:G45)</f>
         <v>2126.2000000000003</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="I47">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G47" s="89">
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I49" s="68">
-        <f>I46-B31</f>
+    <row r="49" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G49" s="90">
+        <f>G46-B31</f>
         <v>0</v>
       </c>
     </row>
@@ -11526,136 +11404,136 @@
   <dimension ref="A1:E8"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="26.85546875" style="92" customWidth="1"/>
-    <col min="2" max="2" width="41.140625" style="92" customWidth="1"/>
-    <col min="3" max="3" width="13.140625" style="92" customWidth="1"/>
-    <col min="4" max="4" width="14.28515625" style="92" customWidth="1"/>
-    <col min="5" max="5" width="15.42578125" style="92" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="92"/>
+    <col min="1" max="1" width="26.85546875" style="77" customWidth="1"/>
+    <col min="2" max="2" width="41.140625" style="77" customWidth="1"/>
+    <col min="3" max="3" width="13.140625" style="77" customWidth="1"/>
+    <col min="4" max="4" width="14.28515625" style="77" customWidth="1"/>
+    <col min="5" max="5" width="15.42578125" style="77" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="77"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="99" t="s">
+      <c r="A1" s="85" t="s">
         <v>91</v>
       </c>
-      <c r="B1" s="100"/>
-      <c r="C1" s="100"/>
-      <c r="D1" s="100"/>
-      <c r="E1" s="101"/>
+      <c r="B1" s="86"/>
+      <c r="C1" s="86"/>
+      <c r="D1" s="86"/>
+      <c r="E1" s="87"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A2" s="84" t="s">
+      <c r="A2" s="69" t="s">
         <v>82</v>
       </c>
-      <c r="B2" s="84" t="s">
+      <c r="B2" s="69" t="s">
         <v>78</v>
       </c>
-      <c r="C2" s="85" t="s">
+      <c r="C2" s="70" t="s">
         <v>79</v>
       </c>
-      <c r="D2" s="85" t="s">
+      <c r="D2" s="70" t="s">
         <v>80</v>
       </c>
-      <c r="E2" s="86" t="s">
+      <c r="E2" s="71" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A3" s="87" t="s">
+      <c r="A3" s="72" t="s">
         <v>70</v>
       </c>
-      <c r="B3" s="88" t="s">
+      <c r="B3" s="73" t="s">
         <v>101</v>
       </c>
-      <c r="C3" s="88" t="s">
+      <c r="C3" s="73" t="s">
         <v>71</v>
       </c>
-      <c r="D3" s="89">
+      <c r="D3" s="74">
         <v>1</v>
       </c>
-      <c r="E3" s="89">
+      <c r="E3" s="74">
         <f>'3пом'!B30</f>
         <v>2056.7999999999997</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A4" s="54" t="s">
+      <c r="A4" s="53" t="s">
         <v>72</v>
       </c>
-      <c r="B4" s="88"/>
-      <c r="C4" s="90" t="s">
+      <c r="B4" s="73"/>
+      <c r="C4" s="75" t="s">
         <v>73</v>
       </c>
-      <c r="D4" s="91">
+      <c r="D4" s="76">
         <v>0.15</v>
       </c>
-      <c r="E4" s="91">
+      <c r="E4" s="76">
         <f>D4*E3</f>
         <v>308.51999999999992</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A5" s="54" t="s">
+      <c r="A5" s="53" t="s">
         <v>74</v>
       </c>
-      <c r="B5" s="88"/>
-      <c r="C5" s="90" t="s">
+      <c r="B5" s="73"/>
+      <c r="C5" s="75" t="s">
         <v>73</v>
       </c>
-      <c r="D5" s="91">
+      <c r="D5" s="76">
         <v>4.5</v>
       </c>
-      <c r="E5" s="91">
+      <c r="E5" s="76">
         <f>D5*E3</f>
         <v>9255.5999999999985</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A6" s="87" t="s">
+      <c r="A6" s="72" t="s">
         <v>75</v>
       </c>
-      <c r="B6" s="88" t="s">
+      <c r="B6" s="73" t="s">
         <v>100</v>
       </c>
-      <c r="C6" s="88" t="s">
+      <c r="C6" s="73" t="s">
         <v>71</v>
       </c>
-      <c r="D6" s="89">
+      <c r="D6" s="74">
         <v>1</v>
       </c>
-      <c r="E6" s="89">
+      <c r="E6" s="74">
         <f>E3</f>
         <v>2056.7999999999997</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A7" s="54" t="s">
+      <c r="A7" s="53" t="s">
         <v>76</v>
       </c>
-      <c r="B7" s="88"/>
-      <c r="C7" s="90" t="s">
+      <c r="B7" s="73"/>
+      <c r="C7" s="75" t="s">
         <v>73</v>
       </c>
-      <c r="D7" s="91">
+      <c r="D7" s="76">
         <v>1.8</v>
       </c>
-      <c r="E7" s="91">
+      <c r="E7" s="76">
         <f>D7*E6</f>
         <v>3702.24</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A8" s="54" t="s">
+      <c r="A8" s="53" t="s">
         <v>77</v>
       </c>
-      <c r="B8" s="88"/>
-      <c r="C8" s="90" t="s">
+      <c r="B8" s="73"/>
+      <c r="C8" s="75" t="s">
         <v>73</v>
       </c>
-      <c r="D8" s="91">
+      <c r="D8" s="76">
         <v>0.15</v>
       </c>
-      <c r="E8" s="91">
+      <c r="E8" s="76">
         <f>D8*E6</f>
         <v>308.51999999999992</v>
       </c>
@@ -11673,247 +11551,247 @@
   <dimension ref="A1:B30"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10" style="81" customWidth="1"/>
-    <col min="2" max="16384" width="9.140625" style="81"/>
+    <col min="1" max="1" width="10" style="66" customWidth="1"/>
+    <col min="2" max="16384" width="9.140625" style="66"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="80" t="s">
-        <v>108</v>
-      </c>
-      <c r="B1" s="80" t="s">
-        <v>109</v>
+      <c r="A1" s="65" t="s">
+        <v>105</v>
+      </c>
+      <c r="B1" s="65" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="50">
+      <c r="A2" s="49">
         <v>3004</v>
       </c>
-      <c r="B2" s="79">
+      <c r="B2" s="64">
         <v>241.1</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="50">
+      <c r="A3" s="49">
         <v>3007</v>
       </c>
-      <c r="B3" s="79">
+      <c r="B3" s="64">
         <v>8.1</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="50">
+      <c r="A4" s="49">
         <v>3009</v>
       </c>
-      <c r="B4" s="79">
+      <c r="B4" s="64">
         <v>22.8</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="50">
+      <c r="A5" s="49">
         <v>3012</v>
       </c>
-      <c r="B5" s="79">
+      <c r="B5" s="64">
         <v>233.5</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="50">
+      <c r="A6" s="49">
         <v>3015</v>
       </c>
-      <c r="B6" s="79">
+      <c r="B6" s="64">
         <v>19.100000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="50">
+      <c r="A7" s="49">
         <v>3017</v>
       </c>
-      <c r="B7" s="79">
+      <c r="B7" s="64">
         <v>9.4</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="50">
+      <c r="A8" s="49">
         <v>3019</v>
       </c>
-      <c r="B8" s="79">
+      <c r="B8" s="64">
         <v>315.5</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="50">
+      <c r="A9" s="49">
         <v>3023</v>
       </c>
-      <c r="B9" s="79">
+      <c r="B9" s="64">
         <v>185.9</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="50">
+      <c r="A10" s="49">
         <v>3033</v>
       </c>
-      <c r="B10" s="79">
+      <c r="B10" s="64">
         <v>8.8999999999999986</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="50">
+      <c r="A11" s="49">
         <v>3037</v>
       </c>
-      <c r="B11" s="79">
+      <c r="B11" s="64">
         <v>111.60000000000001</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="50">
+      <c r="A12" s="49">
         <v>3041</v>
       </c>
-      <c r="B12" s="79">
+      <c r="B12" s="64">
         <v>159.80000000000001</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="50">
+      <c r="A13" s="49">
         <v>3042</v>
       </c>
-      <c r="B13" s="79">
+      <c r="B13" s="64">
         <v>21.4</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="50">
+      <c r="A14" s="49">
         <v>3043</v>
       </c>
-      <c r="B14" s="79">
+      <c r="B14" s="64">
         <v>21.8</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="50">
+      <c r="A15" s="49">
         <v>3045</v>
       </c>
-      <c r="B15" s="79">
+      <c r="B15" s="64">
         <v>4.5999999999999996</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="50">
+      <c r="A16" s="49">
         <v>3046</v>
       </c>
-      <c r="B16" s="79">
+      <c r="B16" s="64">
         <v>9</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="50">
+      <c r="A17" s="49">
         <v>3051</v>
       </c>
-      <c r="B17" s="79">
+      <c r="B17" s="64">
         <v>193.7</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="50">
+      <c r="A18" s="49">
         <v>3053</v>
       </c>
-      <c r="B18" s="79">
+      <c r="B18" s="64">
         <v>198.20000000000002</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="50">
+      <c r="A19" s="49">
         <v>3055</v>
       </c>
-      <c r="B19" s="79">
+      <c r="B19" s="64">
         <v>13.8</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="50">
+      <c r="A20" s="49">
         <v>3057</v>
       </c>
-      <c r="B20" s="79">
+      <c r="B20" s="64">
         <v>8</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="50">
+      <c r="A21" s="49">
         <v>3059</v>
       </c>
-      <c r="B21" s="79">
+      <c r="B21" s="64">
         <v>38.799999999999997</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="50">
+      <c r="A22" s="49">
         <v>3060</v>
       </c>
-      <c r="B22" s="79">
+      <c r="B22" s="64">
         <v>7.5</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="50">
+      <c r="A23" s="49">
         <v>3061</v>
       </c>
-      <c r="B23" s="79">
+      <c r="B23" s="64">
         <v>12</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="50">
+      <c r="A24" s="49">
         <v>3062</v>
       </c>
-      <c r="B24" s="79">
+      <c r="B24" s="64">
         <v>11.5</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="50">
+      <c r="A25" s="49">
         <v>3063</v>
       </c>
-      <c r="B25" s="79">
+      <c r="B25" s="64">
         <v>72</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="50">
+      <c r="A26" s="49">
         <v>3064</v>
       </c>
-      <c r="B26" s="79">
+      <c r="B26" s="64">
         <v>14.6</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" s="50">
+      <c r="A27" s="49">
         <v>3065</v>
       </c>
-      <c r="B27" s="79">
+      <c r="B27" s="64">
         <v>2.3000000000000003</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" s="50">
+      <c r="A28" s="49">
         <v>3066</v>
       </c>
-      <c r="B28" s="79">
+      <c r="B28" s="64">
         <v>97.600000000000009</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" s="50">
+      <c r="A29" s="49">
         <v>3067</v>
       </c>
-      <c r="B29" s="79">
+      <c r="B29" s="64">
         <v>14.299999999999999</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" s="82" t="s">
+      <c r="A30" s="67" t="s">
         <v>93</v>
       </c>
-      <c r="B30" s="83">
+      <c r="B30" s="68">
         <f>SUM(B2:B29)</f>
         <v>2056.7999999999997</v>
       </c>
@@ -11926,1025 +11804,688 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L47"/>
+  <dimension ref="A1:H47"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.28515625" customWidth="1"/>
     <col min="2" max="2" width="14.28515625" customWidth="1"/>
-    <col min="3" max="6" width="9.140625" customWidth="1"/>
-    <col min="12" max="12" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.85546875" customWidth="1"/>
+    <col min="4" max="4" width="9.140625" customWidth="1"/>
+    <col min="5" max="5" width="15.5703125" customWidth="1"/>
+    <col min="8" max="8" width="9.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="70" t="s">
+    <row r="1" spans="1:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="A1" s="48" t="s">
         <v>92</v>
       </c>
-      <c r="B1" s="71" t="s">
-        <v>86</v>
-      </c>
-      <c r="C1" t="s">
-        <v>107</v>
-      </c>
-      <c r="H1" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="63">
+      <c r="B1" s="102" t="s">
+        <v>108</v>
+      </c>
+      <c r="C1" s="95" t="s">
+        <v>112</v>
+      </c>
+      <c r="D1" s="95" t="s">
+        <v>109</v>
+      </c>
+      <c r="E1" s="95" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="103">
         <v>3004</v>
       </c>
-      <c r="B2" s="58">
+      <c r="B2" s="104">
+        <f>'3пом'!B2</f>
         <v>241.1</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="104">
+        <v>244.1</v>
+      </c>
+      <c r="D2" s="95">
         <v>244.9</v>
       </c>
-      <c r="D2" s="68">
-        <f>B2-C2</f>
-        <v>-3.8000000000000114</v>
-      </c>
-      <c r="E2">
-        <f t="shared" ref="E2:E28" si="0">D2/2</f>
-        <v>-1.9000000000000057</v>
-      </c>
-      <c r="G2" s="58">
-        <v>244.1</v>
-      </c>
-      <c r="H2" s="58">
-        <v>244.1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="63">
+      <c r="E2" s="105">
+        <f>C2-D2</f>
+        <v>-0.80000000000001137</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="103">
         <v>3007</v>
       </c>
-      <c r="B3" s="58">
+      <c r="B3" s="104">
+        <f>'3пом'!B3</f>
         <v>8.1</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="104">
         <v>9.1</v>
       </c>
-      <c r="D3" s="68">
-        <f t="shared" ref="D3:D29" si="1">B3-C3</f>
-        <v>-1</v>
-      </c>
-      <c r="E3">
+      <c r="D3" s="95">
+        <v>9.1</v>
+      </c>
+      <c r="E3" s="105">
+        <f t="shared" ref="E3:E29" si="0">C3-D3</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="103">
+        <v>3009</v>
+      </c>
+      <c r="B4" s="104">
+        <f>'3пом'!B4</f>
+        <v>22.8</v>
+      </c>
+      <c r="C4" s="104">
+        <v>23.5</v>
+      </c>
+      <c r="D4" s="95">
+        <v>23.5</v>
+      </c>
+      <c r="E4" s="105">
         <f t="shared" si="0"/>
-        <v>-0.5</v>
-      </c>
-      <c r="G3" s="68">
-        <f t="shared" ref="G3:G29" si="2">B3-E3</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="106">
+        <v>3012</v>
+      </c>
+      <c r="B5" s="107">
+        <f>'3пом'!B5</f>
+        <v>233.5</v>
+      </c>
+      <c r="C5" s="107">
+        <v>470.2</v>
+      </c>
+      <c r="D5" s="108">
+        <v>235.7</v>
+      </c>
+      <c r="E5" s="109">
+        <f t="shared" si="0"/>
+        <v>234.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="103">
+        <v>3015</v>
+      </c>
+      <c r="B6" s="104">
+        <f>'3пом'!B6</f>
+        <v>19.100000000000001</v>
+      </c>
+      <c r="C6" s="104">
+        <v>19.600000000000001</v>
+      </c>
+      <c r="D6" s="95">
+        <v>19.600000000000001</v>
+      </c>
+      <c r="E6" s="105">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="103">
+        <v>3017</v>
+      </c>
+      <c r="B7" s="104">
+        <f>'3пом'!B7</f>
+        <v>9.4</v>
+      </c>
+      <c r="C7" s="104">
+        <v>10.3</v>
+      </c>
+      <c r="D7" s="95">
+        <v>10.3</v>
+      </c>
+      <c r="E7" s="105">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="103">
+        <v>3019</v>
+      </c>
+      <c r="B8" s="104">
+        <f>'3пом'!B8</f>
+        <v>315.5</v>
+      </c>
+      <c r="C8" s="104">
+        <v>321.8</v>
+      </c>
+      <c r="D8" s="95">
+        <v>320.39999999999998</v>
+      </c>
+      <c r="E8" s="105">
+        <f t="shared" si="0"/>
+        <v>1.4000000000000341</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="106">
+        <v>3023</v>
+      </c>
+      <c r="B9" s="107">
+        <f>'3пом'!B9</f>
+        <v>185.9</v>
+      </c>
+      <c r="C9" s="107">
+        <v>364.3</v>
+      </c>
+      <c r="D9" s="108">
+        <v>188.6</v>
+      </c>
+      <c r="E9" s="109">
+        <f t="shared" si="0"/>
+        <v>175.70000000000002</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="103">
+        <v>3033</v>
+      </c>
+      <c r="B10" s="104">
+        <f>'3пом'!B10</f>
+        <v>8.8999999999999986</v>
+      </c>
+      <c r="C10" s="104">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="D10" s="95">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="E10" s="105">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="106">
+        <v>3037</v>
+      </c>
+      <c r="B11" s="107">
+        <f>'3пом'!B11</f>
+        <v>111.60000000000001</v>
+      </c>
+      <c r="C11" s="107">
+        <v>232.5</v>
+      </c>
+      <c r="D11" s="108">
+        <v>116.4</v>
+      </c>
+      <c r="E11" s="109">
+        <f t="shared" si="0"/>
+        <v>116.1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="106">
+        <v>3041</v>
+      </c>
+      <c r="B12" s="107">
+        <f>'3пом'!B12</f>
+        <v>159.80000000000001</v>
+      </c>
+      <c r="C12" s="107">
+        <v>331.2</v>
+      </c>
+      <c r="D12" s="108">
+        <v>165.8</v>
+      </c>
+      <c r="E12" s="109">
+        <f t="shared" si="0"/>
+        <v>165.39999999999998</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="103">
+        <v>3042</v>
+      </c>
+      <c r="B13" s="104">
+        <f>'3пом'!B13</f>
+        <v>21.4</v>
+      </c>
+      <c r="C13" s="104">
+        <v>22.2</v>
+      </c>
+      <c r="D13" s="95">
+        <v>22.2</v>
+      </c>
+      <c r="E13" s="105">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="103">
+        <v>3043</v>
+      </c>
+      <c r="B14" s="104">
+        <f>'3пом'!B14</f>
+        <v>21.8</v>
+      </c>
+      <c r="C14" s="104">
+        <v>22.1</v>
+      </c>
+      <c r="D14" s="95">
+        <v>22.1</v>
+      </c>
+      <c r="E14" s="105">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="103">
+        <v>3045</v>
+      </c>
+      <c r="B15" s="104">
+        <f>'3пом'!B15</f>
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="C15" s="104">
+        <v>5.6</v>
+      </c>
+      <c r="D15" s="95">
+        <v>5.6</v>
+      </c>
+      <c r="E15" s="105">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="103">
+        <v>3046</v>
+      </c>
+      <c r="B16" s="104">
+        <f>'3пом'!B16</f>
+        <v>9</v>
+      </c>
+      <c r="C16" s="104">
+        <v>9.1</v>
+      </c>
+      <c r="D16" s="95">
+        <v>9.1</v>
+      </c>
+      <c r="E16" s="105">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="106">
+        <v>3051</v>
+      </c>
+      <c r="B17" s="107">
+        <f>'3пом'!B17</f>
+        <v>193.7</v>
+      </c>
+      <c r="C17" s="107">
+        <v>363.8</v>
+      </c>
+      <c r="D17" s="108">
+        <v>198.1</v>
+      </c>
+      <c r="E17" s="109">
+        <f t="shared" si="0"/>
+        <v>165.70000000000002</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="103">
+        <v>3053</v>
+      </c>
+      <c r="B18" s="104">
+        <f>'3пом'!B18</f>
+        <v>198.20000000000002</v>
+      </c>
+      <c r="C18" s="104">
+        <v>200.9</v>
+      </c>
+      <c r="D18" s="95">
+        <v>200.9</v>
+      </c>
+      <c r="E18" s="105">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="103">
+        <v>3055</v>
+      </c>
+      <c r="B19" s="104">
+        <f>'3пом'!B19</f>
+        <v>13.8</v>
+      </c>
+      <c r="C19" s="104">
+        <v>14.5</v>
+      </c>
+      <c r="D19" s="95">
+        <v>14.5</v>
+      </c>
+      <c r="E19" s="105">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="103">
+        <v>3057</v>
+      </c>
+      <c r="B20" s="104">
+        <f>'3пом'!B20</f>
+        <v>8</v>
+      </c>
+      <c r="C20" s="104">
         <v>8.6</v>
       </c>
-      <c r="H3" s="58">
-        <v>9.1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="65">
-        <v>3009</v>
-      </c>
-      <c r="B4" s="59">
-        <v>22.8</v>
-      </c>
-      <c r="C4">
-        <v>23.5</v>
-      </c>
-      <c r="D4" s="68">
-        <f t="shared" si="1"/>
-        <v>-0.69999999999999929</v>
-      </c>
-      <c r="E4">
+      <c r="D20" s="95">
+        <v>8.6</v>
+      </c>
+      <c r="E20" s="105">
         <f t="shared" si="0"/>
-        <v>-0.34999999999999964</v>
-      </c>
-      <c r="G4" s="68">
-        <f t="shared" si="2"/>
-        <v>23.15</v>
-      </c>
-      <c r="H4" s="59">
-        <v>23.5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="63">
-        <v>3012</v>
-      </c>
-      <c r="B5" s="58">
-        <v>233.5</v>
-      </c>
-      <c r="C5">
-        <v>235.7</v>
-      </c>
-      <c r="D5" s="68">
-        <f t="shared" si="1"/>
-        <v>-2.1999999999999886</v>
-      </c>
-      <c r="E5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="103">
+        <v>3059</v>
+      </c>
+      <c r="B21" s="104">
+        <f>'3пом'!B21</f>
+        <v>38.799999999999997</v>
+      </c>
+      <c r="C21" s="104">
+        <v>39</v>
+      </c>
+      <c r="D21" s="95">
+        <v>39</v>
+      </c>
+      <c r="E21" s="105">
         <f t="shared" si="0"/>
-        <v>-1.0999999999999943</v>
-      </c>
-      <c r="G5" s="68">
-        <f>B5-E5-40.48</f>
-        <v>194.12</v>
-      </c>
-      <c r="H5" s="58">
-        <v>470.2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="64">
-        <v>3015</v>
-      </c>
-      <c r="B6" s="57">
-        <v>19.100000000000001</v>
-      </c>
-      <c r="C6">
-        <v>19.600000000000001</v>
-      </c>
-      <c r="D6" s="68">
-        <f t="shared" si="1"/>
-        <v>-0.5</v>
-      </c>
-      <c r="E6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="103">
+        <v>3060</v>
+      </c>
+      <c r="B22" s="104">
+        <f>'3пом'!B22</f>
+        <v>7.5</v>
+      </c>
+      <c r="C22" s="104">
+        <v>7.6</v>
+      </c>
+      <c r="D22" s="95">
+        <v>7.6</v>
+      </c>
+      <c r="E22" s="105">
         <f t="shared" si="0"/>
-        <v>-0.25</v>
-      </c>
-      <c r="G6" s="68">
-        <f t="shared" si="2"/>
-        <v>19.350000000000001</v>
-      </c>
-      <c r="H6" s="57">
-        <v>19.600000000000001</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="64">
-        <v>3017</v>
-      </c>
-      <c r="B7" s="57">
-        <v>9.4</v>
-      </c>
-      <c r="C7">
-        <v>10.3</v>
-      </c>
-      <c r="D7" s="68">
-        <f t="shared" si="1"/>
-        <v>-0.90000000000000036</v>
-      </c>
-      <c r="E7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="103">
+        <v>3061</v>
+      </c>
+      <c r="B23" s="104">
+        <f>'3пом'!B23</f>
+        <v>12</v>
+      </c>
+      <c r="C23" s="104">
+        <v>12.8</v>
+      </c>
+      <c r="D23" s="95">
+        <v>12.8</v>
+      </c>
+      <c r="E23" s="105">
         <f t="shared" si="0"/>
-        <v>-0.45000000000000018</v>
-      </c>
-      <c r="G7" s="68">
-        <f t="shared" si="2"/>
-        <v>9.8500000000000014</v>
-      </c>
-      <c r="H7" s="57">
-        <v>10.3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="66">
-        <v>3019</v>
-      </c>
-      <c r="B8" s="61">
-        <v>315.5</v>
-      </c>
-      <c r="C8">
-        <v>320.39999999999998</v>
-      </c>
-      <c r="D8" s="68">
-        <f t="shared" si="1"/>
-        <v>-4.8999999999999773</v>
-      </c>
-      <c r="E8">
-        <f t="shared" si="0"/>
-        <v>-2.4499999999999886</v>
-      </c>
-      <c r="G8" s="68">
-        <f t="shared" si="2"/>
-        <v>317.95</v>
-      </c>
-      <c r="H8" s="61">
-        <v>321.8</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="63">
-        <v>3023</v>
-      </c>
-      <c r="B9" s="58">
-        <v>185.9</v>
-      </c>
-      <c r="C9">
-        <v>188.6</v>
-      </c>
-      <c r="D9" s="68">
-        <f t="shared" si="1"/>
-        <v>-2.6999999999999886</v>
-      </c>
-      <c r="E9">
-        <f t="shared" si="0"/>
-        <v>-1.3499999999999943</v>
-      </c>
-      <c r="G9" s="68">
-        <f t="shared" si="2"/>
-        <v>187.25</v>
-      </c>
-      <c r="H9" s="58">
-        <v>364.3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="63">
-        <v>3033</v>
-      </c>
-      <c r="B10" s="58">
-        <v>8.8999999999999986</v>
-      </c>
-      <c r="C10">
-        <v>9.1999999999999993</v>
-      </c>
-      <c r="D10" s="68">
-        <f t="shared" si="1"/>
-        <v>-0.30000000000000071</v>
-      </c>
-      <c r="E10">
-        <f t="shared" si="0"/>
-        <v>-0.15000000000000036</v>
-      </c>
-      <c r="G10" s="68">
-        <f t="shared" si="2"/>
-        <v>9.0499999999999989</v>
-      </c>
-      <c r="H10" s="58">
-        <v>9.1999999999999993</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="66">
-        <v>3037</v>
-      </c>
-      <c r="B11" s="61">
-        <v>111.60000000000001</v>
-      </c>
-      <c r="C11">
-        <v>116.4</v>
-      </c>
-      <c r="D11" s="68">
-        <f t="shared" si="1"/>
-        <v>-4.7999999999999972</v>
-      </c>
-      <c r="E11">
-        <f t="shared" si="0"/>
-        <v>-2.3999999999999986</v>
-      </c>
-      <c r="G11" s="68">
-        <f t="shared" si="2"/>
-        <v>114</v>
-      </c>
-      <c r="H11" s="61">
-        <v>232.5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="64">
-        <v>3041</v>
-      </c>
-      <c r="B12" s="57">
-        <v>159.80000000000001</v>
-      </c>
-      <c r="C12">
-        <v>165.8</v>
-      </c>
-      <c r="D12" s="68">
-        <f t="shared" si="1"/>
-        <v>-6</v>
-      </c>
-      <c r="E12">
-        <f t="shared" si="0"/>
-        <v>-3</v>
-      </c>
-      <c r="G12" s="68">
-        <f t="shared" si="2"/>
-        <v>162.80000000000001</v>
-      </c>
-      <c r="H12" s="57">
-        <v>331.2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="63">
-        <v>3042</v>
-      </c>
-      <c r="B13" s="58">
-        <v>21.4</v>
-      </c>
-      <c r="C13">
-        <v>22.2</v>
-      </c>
-      <c r="D13" s="68">
-        <f t="shared" si="1"/>
-        <v>-0.80000000000000071</v>
-      </c>
-      <c r="E13">
-        <f t="shared" si="0"/>
-        <v>-0.40000000000000036</v>
-      </c>
-      <c r="G13" s="68">
-        <f t="shared" si="2"/>
-        <v>21.799999999999997</v>
-      </c>
-      <c r="H13" s="58">
-        <v>22.2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="64">
-        <v>3043</v>
-      </c>
-      <c r="B14" s="57">
-        <v>21.8</v>
-      </c>
-      <c r="C14">
-        <v>22.1</v>
-      </c>
-      <c r="D14" s="68">
-        <f t="shared" si="1"/>
-        <v>-0.30000000000000071</v>
-      </c>
-      <c r="E14">
-        <f t="shared" si="0"/>
-        <v>-0.15000000000000036</v>
-      </c>
-      <c r="G14" s="68">
-        <f t="shared" si="2"/>
-        <v>21.950000000000003</v>
-      </c>
-      <c r="H14" s="57">
-        <v>22.1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="63">
-        <v>3045</v>
-      </c>
-      <c r="B15" s="58">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="C15">
-        <v>5.6</v>
-      </c>
-      <c r="D15" s="68">
-        <f t="shared" si="1"/>
-        <v>-1</v>
-      </c>
-      <c r="E15">
-        <f t="shared" si="0"/>
-        <v>-0.5</v>
-      </c>
-      <c r="G15" s="68">
-        <f t="shared" si="2"/>
-        <v>5.0999999999999996</v>
-      </c>
-      <c r="H15" s="58">
-        <v>5.6</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="64">
-        <v>3046</v>
-      </c>
-      <c r="B16" s="57">
-        <v>9</v>
-      </c>
-      <c r="C16">
-        <v>9.1</v>
-      </c>
-      <c r="D16" s="68">
-        <f t="shared" si="1"/>
-        <v>-9.9999999999999645E-2</v>
-      </c>
-      <c r="E16">
-        <f t="shared" si="0"/>
-        <v>-4.9999999999999822E-2</v>
-      </c>
-      <c r="G16" s="68">
-        <f t="shared" si="2"/>
-        <v>9.0500000000000007</v>
-      </c>
-      <c r="H16" s="57">
-        <v>9.1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="64">
-        <v>3051</v>
-      </c>
-      <c r="B17" s="57">
-        <v>193.7</v>
-      </c>
-      <c r="C17">
-        <v>198.1</v>
-      </c>
-      <c r="D17" s="68">
-        <f t="shared" si="1"/>
-        <v>-4.4000000000000057</v>
-      </c>
-      <c r="E17">
-        <f t="shared" si="0"/>
-        <v>-2.2000000000000028</v>
-      </c>
-      <c r="G17" s="68">
-        <f t="shared" si="2"/>
-        <v>195.89999999999998</v>
-      </c>
-      <c r="H17" s="57">
-        <v>363.8</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="64">
-        <v>3053</v>
-      </c>
-      <c r="B18" s="57">
-        <v>198.20000000000002</v>
-      </c>
-      <c r="C18">
-        <v>200.9</v>
-      </c>
-      <c r="D18" s="68">
-        <f t="shared" si="1"/>
-        <v>-2.6999999999999886</v>
-      </c>
-      <c r="E18">
-        <f t="shared" si="0"/>
-        <v>-1.3499999999999943</v>
-      </c>
-      <c r="G18" s="68">
-        <f t="shared" si="2"/>
-        <v>199.55</v>
-      </c>
-      <c r="H18" s="57">
-        <v>200.9</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="63">
-        <v>3055</v>
-      </c>
-      <c r="B19" s="58">
-        <v>13.8</v>
-      </c>
-      <c r="C19">
-        <v>14.5</v>
-      </c>
-      <c r="D19" s="68">
-        <f t="shared" si="1"/>
-        <v>-0.69999999999999929</v>
-      </c>
-      <c r="E19">
-        <f t="shared" si="0"/>
-        <v>-0.34999999999999964</v>
-      </c>
-      <c r="G19" s="68">
-        <f t="shared" si="2"/>
-        <v>14.15</v>
-      </c>
-      <c r="H19" s="58">
-        <v>14.5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="65">
-        <v>3057</v>
-      </c>
-      <c r="B20" s="59">
-        <v>8</v>
-      </c>
-      <c r="C20">
-        <v>8.6</v>
-      </c>
-      <c r="D20" s="68">
-        <f t="shared" si="1"/>
-        <v>-0.59999999999999964</v>
-      </c>
-      <c r="E20">
-        <f t="shared" si="0"/>
-        <v>-0.29999999999999982</v>
-      </c>
-      <c r="G20" s="68">
-        <f t="shared" si="2"/>
-        <v>8.3000000000000007</v>
-      </c>
-      <c r="H20" s="59">
-        <v>8.6</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="63">
-        <v>3059</v>
-      </c>
-      <c r="B21" s="58">
-        <v>38.799999999999997</v>
-      </c>
-      <c r="C21">
-        <v>39</v>
-      </c>
-      <c r="D21" s="68">
-        <f t="shared" si="1"/>
-        <v>-0.20000000000000284</v>
-      </c>
-      <c r="E21">
-        <f t="shared" si="0"/>
-        <v>-0.10000000000000142</v>
-      </c>
-      <c r="G21" s="68">
-        <f t="shared" si="2"/>
-        <v>38.9</v>
-      </c>
-      <c r="H21" s="58">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="64">
-        <v>3060</v>
-      </c>
-      <c r="B22" s="57">
-        <v>7.5</v>
-      </c>
-      <c r="C22">
-        <v>7.6</v>
-      </c>
-      <c r="D22" s="68">
-        <f t="shared" si="1"/>
-        <v>-9.9999999999999645E-2</v>
-      </c>
-      <c r="E22">
-        <f t="shared" si="0"/>
-        <v>-4.9999999999999822E-2</v>
-      </c>
-      <c r="G22" s="68">
-        <f t="shared" si="2"/>
-        <v>7.55</v>
-      </c>
-      <c r="H22" s="57">
-        <v>7.6</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="63">
-        <v>3061</v>
-      </c>
-      <c r="B23" s="58">
-        <v>12</v>
-      </c>
-      <c r="C23">
-        <v>12.8</v>
-      </c>
-      <c r="D23" s="68">
-        <f t="shared" si="1"/>
-        <v>-0.80000000000000071</v>
-      </c>
-      <c r="E23">
-        <f t="shared" si="0"/>
-        <v>-0.40000000000000036</v>
-      </c>
-      <c r="G23" s="68">
-        <f t="shared" si="2"/>
-        <v>12.4</v>
-      </c>
-      <c r="H23" s="58">
-        <v>12.8</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="103">
         <v>3062</v>
       </c>
-      <c r="B24" s="57">
+      <c r="B24" s="104">
+        <f>'3пом'!B24</f>
         <v>11.5</v>
       </c>
-      <c r="C24" s="68">
+      <c r="C24" s="104">
+        <v>11.8</v>
+      </c>
+      <c r="D24" s="105">
         <f>B24</f>
         <v>11.5</v>
       </c>
-      <c r="D24" s="68">
+      <c r="E24" s="105">
+        <f t="shared" si="0"/>
+        <v>0.30000000000000071</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="103">
+        <v>3063</v>
+      </c>
+      <c r="B25" s="104">
+        <f>'3пом'!B25</f>
+        <v>72</v>
+      </c>
+      <c r="C25" s="104">
+        <v>72.8</v>
+      </c>
+      <c r="D25" s="105">
+        <f t="shared" ref="D25:D27" si="1">B25</f>
+        <v>72</v>
+      </c>
+      <c r="E25" s="105">
+        <f t="shared" si="0"/>
+        <v>0.79999999999999716</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="103">
+        <v>3064</v>
+      </c>
+      <c r="B26" s="104">
+        <f>'3пом'!B26</f>
+        <v>14.6</v>
+      </c>
+      <c r="C26" s="104">
+        <v>15.6</v>
+      </c>
+      <c r="D26" s="105">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="E24">
+        <v>14.6</v>
+      </c>
+      <c r="E26" s="105">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G24" s="68">
-        <f t="shared" si="2"/>
-        <v>11.5</v>
-      </c>
-      <c r="H24" s="57">
-        <v>11.8</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="63">
-        <v>3063</v>
-      </c>
-      <c r="B25" s="58">
-        <v>72</v>
-      </c>
-      <c r="C25" s="68">
-        <f t="shared" ref="B25:C27" si="3">B25</f>
-        <v>72</v>
-      </c>
-      <c r="D25" s="68">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" s="103">
+        <v>3065</v>
+      </c>
+      <c r="B27" s="104">
+        <f>'3пом'!B27</f>
+        <v>2.3000000000000003</v>
+      </c>
+      <c r="C27" s="104">
+        <v>3.2</v>
+      </c>
+      <c r="D27" s="105">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="E25">
+        <v>2.3000000000000003</v>
+      </c>
+      <c r="E27" s="105">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G25" s="68">
-        <f t="shared" si="2"/>
-        <v>72</v>
-      </c>
-      <c r="H25" s="58">
-        <v>72.8</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="64">
-        <v>3064</v>
-      </c>
-      <c r="B26" s="57">
-        <v>14.6</v>
-      </c>
-      <c r="C26" s="68">
-        <f t="shared" si="3"/>
-        <v>14.6</v>
-      </c>
-      <c r="D26" s="68">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="E26">
+        <v>0.89999999999999991</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" s="103">
+        <v>3066</v>
+      </c>
+      <c r="B28" s="104">
+        <f>'3пом'!B28</f>
+        <v>97.600000000000009</v>
+      </c>
+      <c r="C28" s="104">
+        <v>102.2</v>
+      </c>
+      <c r="D28" s="95">
+        <v>101.7</v>
+      </c>
+      <c r="E28" s="105">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G26" s="68">
-        <f t="shared" si="2"/>
-        <v>14.6</v>
-      </c>
-      <c r="H26" s="57">
-        <v>15.6</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="63">
-        <v>3065</v>
-      </c>
-      <c r="B27" s="58">
-        <v>2.3000000000000003</v>
-      </c>
-      <c r="C27" s="68">
-        <f t="shared" si="3"/>
-        <v>2.3000000000000003</v>
-      </c>
-      <c r="D27" s="68">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="E27">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" s="103">
+        <v>3067</v>
+      </c>
+      <c r="B29" s="104">
+        <f>'3пом'!B29</f>
+        <v>14.299999999999999</v>
+      </c>
+      <c r="C29" s="104">
+        <v>15.3</v>
+      </c>
+      <c r="D29" s="95">
+        <v>15.2</v>
+      </c>
+      <c r="E29" s="105">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G27" s="68">
-        <f t="shared" si="2"/>
-        <v>2.3000000000000003</v>
-      </c>
-      <c r="H27" s="58">
-        <v>3.2</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="65">
-        <v>3066</v>
-      </c>
-      <c r="B28" s="59">
-        <v>97.600000000000009</v>
-      </c>
-      <c r="C28">
-        <v>101.7</v>
-      </c>
-      <c r="D28" s="68">
-        <f t="shared" si="1"/>
-        <v>-4.0999999999999943</v>
-      </c>
-      <c r="E28">
-        <f t="shared" si="0"/>
-        <v>-2.0499999999999972</v>
-      </c>
-      <c r="G28" s="68">
-        <f t="shared" si="2"/>
-        <v>99.65</v>
-      </c>
-      <c r="H28" s="59">
-        <v>102.2</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="67">
-        <v>3067</v>
-      </c>
-      <c r="B29" s="60">
-        <v>14.299999999999999</v>
-      </c>
-      <c r="C29">
-        <v>15.2</v>
-      </c>
-      <c r="D29" s="68">
-        <f t="shared" si="1"/>
-        <v>-0.90000000000000036</v>
-      </c>
-      <c r="E29">
-        <f>D29/2</f>
-        <v>-0.45000000000000018</v>
-      </c>
-      <c r="G29" s="68">
-        <f t="shared" si="2"/>
-        <v>14.75</v>
-      </c>
-      <c r="H29" s="60">
-        <v>15.3</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B30" s="68">
+        <v>0.10000000000000142</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B30" s="57">
         <f>SUM(B2:B29)</f>
         <v>2056.7999999999997</v>
       </c>
-      <c r="C30" s="68">
-        <f t="shared" ref="C30:D30" si="4">SUM(C2:C29)</f>
+      <c r="D30" s="57">
+        <f t="shared" ref="D30" si="2">SUM(D2:D29)</f>
         <v>2101.2999999999993</v>
       </c>
-      <c r="D30" s="68">
-        <f t="shared" si="4"/>
-        <v>-44.49999999999995</v>
-      </c>
-      <c r="E30" s="68">
-        <f>SUM(E2:E29)</f>
-        <v>-22.249999999999975</v>
-      </c>
-      <c r="G30" s="68">
-        <f>SUM(G2:G29)</f>
-        <v>2039.67</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="C31" s="53">
-        <v>2789.37</v>
-      </c>
-      <c r="D31" s="69">
-        <f>B30-C31</f>
-        <v>-732.57000000000016</v>
-      </c>
-      <c r="G31" s="78">
-        <f>C31</f>
-        <v>2789.37</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="G32" s="69">
-        <f>G30-G31</f>
-        <v>-749.69999999999982</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="76">
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D31" s="101"/>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" s="62">
         <v>3006</v>
       </c>
-      <c r="B33" s="77">
-        <v>52</v>
-      </c>
-      <c r="C33">
-        <v>31.5</v>
-      </c>
-      <c r="D33" s="68">
-        <f>B33-C33</f>
-        <v>20.5</v>
-      </c>
-      <c r="E33">
-        <f>D33/2</f>
-        <v>10.25</v>
-      </c>
-      <c r="G33" s="68">
-        <f>B33-E33</f>
-        <v>41.75</v>
-      </c>
-    </row>
-    <row r="34" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="72">
+      <c r="B33" s="63"/>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" s="58">
         <v>3016</v>
       </c>
-      <c r="B34" s="73">
-        <v>58.5</v>
-      </c>
-      <c r="C34">
-        <v>38</v>
-      </c>
-      <c r="D34" s="68">
-        <f>B34-C34</f>
-        <v>20.5</v>
-      </c>
-      <c r="E34">
-        <f>D34/2</f>
-        <v>10.25</v>
-      </c>
-      <c r="G34" s="68">
-        <f>B34-E34</f>
-        <v>48.25</v>
-      </c>
-    </row>
-    <row r="35" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="76">
+      <c r="B34" s="59"/>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" s="62">
         <v>3020</v>
       </c>
-      <c r="B35" s="77">
-        <v>49</v>
-      </c>
-      <c r="C35">
-        <v>28.5</v>
-      </c>
-      <c r="D35" s="68">
-        <f>B35-C35</f>
-        <v>20.5</v>
-      </c>
-      <c r="E35">
-        <f>D35/2</f>
-        <v>10.25</v>
-      </c>
-      <c r="G35" s="68">
-        <f>B35-E35</f>
-        <v>38.75</v>
-      </c>
-    </row>
-    <row r="36" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="76">
+      <c r="B35" s="63"/>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" s="62">
         <v>3024</v>
       </c>
-      <c r="B36" s="77">
-        <v>49</v>
-      </c>
-      <c r="C36">
-        <v>28.9</v>
-      </c>
-      <c r="D36" s="68">
-        <f>B36-C36</f>
-        <v>20.100000000000001</v>
-      </c>
-      <c r="E36">
-        <f>D36/2</f>
-        <v>10.050000000000001</v>
-      </c>
-      <c r="G36" s="68">
-        <f>B36-E36</f>
-        <v>38.950000000000003</v>
-      </c>
-    </row>
-    <row r="37" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="76">
+      <c r="B36" s="63"/>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" s="62">
         <v>3034</v>
       </c>
-      <c r="B37" s="77">
-        <v>55.2</v>
-      </c>
-      <c r="C37">
-        <v>34.700000000000003</v>
-      </c>
-      <c r="D37" s="68">
-        <f>B37-C37</f>
-        <v>20.5</v>
-      </c>
-      <c r="E37">
-        <f>D37/2</f>
-        <v>10.25</v>
-      </c>
-      <c r="G37" s="68">
-        <f>B37-E37</f>
-        <v>44.95</v>
-      </c>
-    </row>
-    <row r="38" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="74">
+      <c r="B37" s="63"/>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" s="60">
         <v>3047</v>
       </c>
-      <c r="B38" s="75">
-        <v>54.4</v>
-      </c>
-      <c r="C38">
-        <v>33.9</v>
-      </c>
-      <c r="D38" s="68">
-        <f>B38-C38</f>
-        <v>20.5</v>
-      </c>
-      <c r="E38">
-        <f>D38/2</f>
-        <v>10.25</v>
-      </c>
-      <c r="G38" s="68">
-        <f>B38-E38</f>
-        <v>44.15</v>
-      </c>
-    </row>
-    <row r="39" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="72">
+      <c r="B38" s="61"/>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" s="58">
         <v>3052</v>
       </c>
-      <c r="B39" s="73">
-        <v>50.1</v>
-      </c>
-      <c r="C39">
-        <v>29.6</v>
-      </c>
-      <c r="D39" s="68">
-        <f>B39-C39</f>
-        <v>20.5</v>
-      </c>
-      <c r="E39">
-        <f>D39/2</f>
-        <v>10.25</v>
-      </c>
-      <c r="G39" s="68">
-        <f>B39-E39</f>
-        <v>39.85</v>
-      </c>
-    </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="K40" t="s">
+      <c r="B39" s="59"/>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G40" t="s">
         <v>94</v>
       </c>
-      <c r="L40" s="68">
+      <c r="H40" s="57">
         <f>B17+B18+B21+B22+B23+B24</f>
         <v>461.7</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="K41" t="s">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G41" t="s">
         <v>95</v>
       </c>
-      <c r="L41" s="68">
+      <c r="H41" s="57">
         <f>SUM(B11:B16)+B27</f>
         <v>330.50000000000006</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="K42" t="s">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G42" t="s">
         <v>96</v>
       </c>
-      <c r="L42" s="104">
+      <c r="H42" s="81">
         <f>B10+B28+B19+B20+B26</f>
         <v>142.9</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="K43" t="s">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G43" t="s">
         <v>97</v>
       </c>
-      <c r="L43" s="68">
+      <c r="H43" s="57">
         <f>B8+B9+B25</f>
         <v>573.4</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="K44" t="s">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G44" t="s">
         <v>98</v>
       </c>
-      <c r="L44" s="68">
+      <c r="H44" s="57">
         <f>SUM(B5:B7)+B29</f>
         <v>276.3</v>
       </c>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="K45" t="s">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G45" t="s">
         <v>99</v>
       </c>
-      <c r="L45" s="68">
+      <c r="H45" s="57">
         <f>SUM(B2:B4)</f>
         <v>272</v>
       </c>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="L46" s="68">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H46" s="57">
         <f>B30</f>
         <v>2056.7999999999997</v>
       </c>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="L47" s="68">
-        <f>SUM(L40:L45)-L46</f>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H47" s="57">
+        <f>SUM(H40:H45)-H46</f>
         <v>0</v>
       </c>
     </row>
